--- a/output/CLOTH01_summer/feeds_excel/simulation feeds/CustomerOrderDelivery.xlsx
+++ b/output/CLOTH01_summer/feeds_excel/simulation feeds/CustomerOrderDelivery.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G268"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,12 +508,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -545,12 +545,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -582,12 +582,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1344,27 +1344,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240403_STORE_001_000005</t>
+          <t>DN_CLOTH01_20240403_STORE_002_000006</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240403_STORE_001_0005</t>
+          <t>CO_CLOTH01_20240403_STORE_002_0006</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1522,44 +1522,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240403_STORE_002_000006</t>
+          <t>DN_CLOTH01_20240404_STORE_001_000007</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240403_STORE_002_0006</t>
+          <t>CO_CLOTH01_20240404_STORE_001_0007</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2024-04-03 00:00:00</t>
+          <t>2024-04-04 00:00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1707,44 +1707,44 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240404_STORE_001_000007</t>
+          <t>DN_CLOTH01_20240404_STORE_002_000008</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240404_STORE_001_0007</t>
+          <t>CO_CLOTH01_20240404_STORE_002_0008</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2024-04-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2024-04-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1877,22 +1877,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2024-04-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2024-04-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2565,74 +2565,74 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240407_STORE_001_000013</t>
+          <t>DN_CLOTH01_20240406_STORE_002_000012</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240407_STORE_001_0013</t>
+          <t>CO_CLOTH01_20240406_STORE_002_0012</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2024-04-07 00:00:00</t>
+          <t>2024-04-06 00:00:00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240407_STORE_001_000013</t>
+          <t>DN_CLOTH01_20240406_STORE_002_000012</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240407_STORE_001_0013</t>
+          <t>CO_CLOTH01_20240406_STORE_002_0012</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2024-04-07 00:00:00</t>
+          <t>2024-04-06 00:00:00</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2728,49 +2728,49 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2024-04-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2024-04-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240407_STORE_002_000014</t>
+          <t>DN_CLOTH01_20240407_STORE_001_000013</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240407_STORE_002_0014</t>
+          <t>CO_CLOTH01_20240407_STORE_001_0013</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2780,34 +2780,34 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240407_STORE_002_000014</t>
+          <t>DN_CLOTH01_20240407_STORE_001_000013</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240407_STORE_002_0014</t>
+          <t>CO_CLOTH01_20240407_STORE_001_0013</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2928,81 +2928,81 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240408_STORE_001_000015</t>
+          <t>DN_CLOTH01_20240407_STORE_002_000014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240408_STORE_001_0015</t>
+          <t>CO_CLOTH01_20240407_STORE_002_0014</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2024-04-08 00:00:00</t>
+          <t>2024-04-07 00:00:00</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240408_STORE_001_000015</t>
+          <t>DN_CLOTH01_20240407_STORE_002_000014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240408_STORE_001_0015</t>
+          <t>CO_CLOTH01_20240407_STORE_002_0014</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2024-04-08 00:00:00</t>
+          <t>2024-04-07 00:00:00</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3039,34 +3039,34 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
+          <t>DN_CLOTH01_20240408_STORE_001_000015</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
+          <t>CO_CLOTH01_20240408_STORE_001_0015</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
+          <t>DN_CLOTH01_20240408_STORE_001_000015</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
+          <t>CO_CLOTH01_20240408_STORE_001_0015</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3113,34 +3113,34 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
+          <t>DN_CLOTH01_20240408_STORE_001_000015</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
+          <t>CO_CLOTH01_20240408_STORE_001_0015</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3150,34 +3150,34 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
+          <t>DN_CLOTH01_20240408_STORE_001_000015</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
+          <t>CO_CLOTH01_20240408_STORE_001_0015</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3187,39 +3187,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
+          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
+          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2024-04-09 00:00:00</t>
+          <t>2024-04-08 00:00:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3231,32 +3231,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
+          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
+          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2024-04-09 00:00:00</t>
+          <t>2024-04-08 00:00:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3268,22 +3268,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
+          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
+          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2024-04-09 00:00:00</t>
+          <t>2024-04-08 00:00:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3305,32 +3305,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
+          <t>DN_CLOTH01_20240408_STORE_002_000016</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
+          <t>CO_CLOTH01_20240408_STORE_002_0016</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2024-04-09 00:00:00</t>
+          <t>2024-04-08 00:00:00</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3372,34 +3372,34 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
+          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
+          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3409,34 +3409,34 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
+          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
+          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3446,34 +3446,34 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
+          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
+          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3483,34 +3483,34 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
+          <t>DN_CLOTH01_20240409_STORE_001_000017</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
+          <t>CO_CLOTH01_20240409_STORE_001_0017</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3557,182 +3557,182 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
+          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
+          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2024-04-10 00:00:00</t>
+          <t>2024-04-09 00:00:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
+          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
+          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2024-04-10 00:00:00</t>
+          <t>2024-04-09 00:00:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
+          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
+          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2024-04-10 00:00:00</t>
+          <t>2024-04-09 00:00:00</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
+          <t>DN_CLOTH01_20240409_STORE_002_000018</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
+          <t>CO_CLOTH01_20240409_STORE_002_0018</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2024-04-10 00:00:00</t>
+          <t>2024-04-09 00:00:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
+          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
+          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3749,27 +3749,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
+          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
+          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3786,27 +3786,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
+          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
+          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3823,27 +3823,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
+          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
+          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3860,27 +3860,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
+          <t>DN_CLOTH01_20240410_STORE_001_000019</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
+          <t>CO_CLOTH01_20240410_STORE_001_0019</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3897,32 +3897,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
+          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
+          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2024-04-11 00:00:00</t>
+          <t>2024-04-10 00:00:00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3934,32 +3934,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
+          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
+          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2024-04-11 00:00:00</t>
+          <t>2024-04-10 00:00:00</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3971,32 +3971,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
+          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
+          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2024-04-11 00:00:00</t>
+          <t>2024-04-10 00:00:00</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4008,32 +4008,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
+          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
+          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2024-04-11 00:00:00</t>
+          <t>2024-04-10 00:00:00</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4045,32 +4045,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
+          <t>DN_CLOTH01_20240410_STORE_002_000020</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
+          <t>CO_CLOTH01_20240410_STORE_002_0020</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2024-04-11 00:00:00</t>
+          <t>2024-04-10 00:00:00</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4082,22 +4082,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
+          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
+          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4119,27 +4119,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
+          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
+          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4156,27 +4156,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
+          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
+          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4193,27 +4193,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
+          <t>DN_CLOTH01_20240411_STORE_001_000021</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
+          <t>CO_CLOTH01_20240411_STORE_001_0021</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4245,155 +4245,155 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2024-04-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2024-04-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
+          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
+          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2024-04-12 00:00:00</t>
+          <t>2024-04-11 00:00:00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
+          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
+          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2024-04-12 00:00:00</t>
+          <t>2024-04-11 00:00:00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
+          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
+          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2024-04-12 00:00:00</t>
+          <t>2024-04-11 00:00:00</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
+          <t>DN_CLOTH01_20240411_STORE_002_000022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
+          <t>CO_CLOTH01_20240411_STORE_002_0022</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2024-04-12 00:00:00</t>
+          <t>2024-04-11 00:00:00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4430,12 +4430,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4445,34 +4445,34 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
+          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
+          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4482,34 +4482,34 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
+          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
+          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4519,34 +4519,34 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
+          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
+          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4556,44 +4556,44 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
+          <t>DN_CLOTH01_20240412_STORE_001_000023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
+          <t>CO_CLOTH01_20240412_STORE_001_0023</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2024-04-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2024-04-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4630,140 +4630,140 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
+          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
+          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2024-04-13 00:00:00</t>
+          <t>2024-04-12 00:00:00</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
+          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
+          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2024-04-13 00:00:00</t>
+          <t>2024-04-12 00:00:00</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
+          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
+          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2024-04-13 00:00:00</t>
+          <t>2024-04-12 00:00:00</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
+          <t>DN_CLOTH01_20240412_STORE_002_000024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
+          <t>CO_CLOTH01_20240412_STORE_002_0024</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2024-04-13 00:00:00</t>
+          <t>2024-04-12 00:00:00</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4800,12 +4800,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4815,34 +4815,34 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
+          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
+          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4852,34 +4852,34 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
+          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
+          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4889,34 +4889,34 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
+          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
+          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4926,34 +4926,34 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
+          <t>DN_CLOTH01_20240413_STORE_001_000025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
+          <t>CO_CLOTH01_20240413_STORE_001_0025</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5000,155 +5000,155 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
+          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
+          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2024-04-14 00:00:00</t>
+          <t>2024-04-13 00:00:00</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
+          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
+          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2024-04-14 00:00:00</t>
+          <t>2024-04-13 00:00:00</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
+          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
+          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2024-04-14 00:00:00</t>
+          <t>2024-04-13 00:00:00</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
+          <t>DN_CLOTH01_20240413_STORE_002_000026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
+          <t>CO_CLOTH01_20240413_STORE_002_0026</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2024-04-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2024-04-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5185,34 +5185,34 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
+          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
+          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5222,34 +5222,34 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
+          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
+          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5259,34 +5259,34 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
+          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
+          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5296,34 +5296,34 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
+          <t>DN_CLOTH01_20240414_STORE_001_000027</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
+          <t>CO_CLOTH01_20240414_STORE_001_0027</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5355,12 +5355,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5370,155 +5370,155 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
+          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
+          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-14 00:00:00</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
+          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
+          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-14 00:00:00</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
+          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
+          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-14 00:00:00</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
+          <t>DN_CLOTH01_20240414_STORE_002_000028</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
+          <t>CO_CLOTH01_20240414_STORE_002_0028</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2024-04-14 00:00:00</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5555,34 +5555,34 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
+          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
+          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5592,34 +5592,34 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
+          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
+          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5629,34 +5629,34 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
+          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
+          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5666,29 +5666,29 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
+          <t>DN_CLOTH01_20240415_STORE_001_000029</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
+          <t>CO_CLOTH01_20240415_STORE_001_0029</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5740,155 +5740,155 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240416_STORE_001_000031</t>
+          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240416_STORE_001_0031</t>
+          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-15 00:00:00</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240416_STORE_001_000031</t>
+          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240416_STORE_001_0031</t>
+          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-15 00:00:00</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240416_STORE_001_000031</t>
+          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240416_STORE_001_0031</t>
+          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-15 00:00:00</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240416_STORE_001_000031</t>
+          <t>DN_CLOTH01_20240415_STORE_002_000030</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240416_STORE_001_0031</t>
+          <t>CO_CLOTH01_20240415_STORE_002_0030</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2024-04-16 00:00:00</t>
+          <t>2024-04-15 00:00:00</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5910,12 +5910,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5925,34 +5925,34 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240416_STORE_002_000032</t>
+          <t>DN_CLOTH01_20240416_STORE_001_000031</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240416_STORE_002_0032</t>
+          <t>CO_CLOTH01_20240416_STORE_001_0031</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5962,34 +5962,34 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240416_STORE_002_000032</t>
+          <t>DN_CLOTH01_20240416_STORE_001_000031</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240416_STORE_002_0032</t>
+          <t>CO_CLOTH01_20240416_STORE_001_0031</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5999,34 +5999,34 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240416_STORE_002_000032</t>
+          <t>DN_CLOTH01_20240416_STORE_001_000031</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240416_STORE_002_0032</t>
+          <t>CO_CLOTH01_20240416_STORE_001_0031</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6058,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6110,118 +6110,118 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240417_STORE_001_000033</t>
+          <t>DN_CLOTH01_20240416_STORE_002_000032</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240417_STORE_001_0033</t>
+          <t>CO_CLOTH01_20240416_STORE_002_0032</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2024-04-17 00:00:00</t>
+          <t>2024-04-16 00:00:00</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240417_STORE_001_000033</t>
+          <t>DN_CLOTH01_20240416_STORE_002_000032</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240417_STORE_001_0033</t>
+          <t>CO_CLOTH01_20240416_STORE_002_0032</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2024-04-17 00:00:00</t>
+          <t>2024-04-16 00:00:00</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240417_STORE_001_000033</t>
+          <t>DN_CLOTH01_20240416_STORE_002_000032</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240417_STORE_001_0033</t>
+          <t>CO_CLOTH01_20240416_STORE_002_0032</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2024-04-17 00:00:00</t>
+          <t>2024-04-16 00:00:00</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6243,12 +6243,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6295,34 +6295,34 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240417_STORE_002_000034</t>
+          <t>DN_CLOTH01_20240417_STORE_001_000033</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240417_STORE_002_0034</t>
+          <t>CO_CLOTH01_20240417_STORE_001_0033</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6332,34 +6332,34 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240417_STORE_002_000034</t>
+          <t>DN_CLOTH01_20240417_STORE_001_000033</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240417_STORE_002_0034</t>
+          <t>CO_CLOTH01_20240417_STORE_001_0033</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6369,44 +6369,44 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240417_STORE_002_000034</t>
+          <t>DN_CLOTH01_20240417_STORE_001_000033</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240417_STORE_002_0034</t>
+          <t>CO_CLOTH01_20240417_STORE_001_0033</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2024-04-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2024-04-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6465,12 +6465,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6480,118 +6480,118 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240418_STORE_001_000035</t>
+          <t>DN_CLOTH01_20240417_STORE_002_000034</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240418_STORE_001_0035</t>
+          <t>CO_CLOTH01_20240417_STORE_002_0034</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2024-04-18 00:00:00</t>
+          <t>2024-04-17 00:00:00</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240418_STORE_001_000035</t>
+          <t>DN_CLOTH01_20240417_STORE_002_000034</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240418_STORE_001_0035</t>
+          <t>CO_CLOTH01_20240417_STORE_002_0034</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2024-04-18 00:00:00</t>
+          <t>2024-04-17 00:00:00</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240418_STORE_001_000035</t>
+          <t>DN_CLOTH01_20240417_STORE_002_000034</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240418_STORE_001_0035</t>
+          <t>CO_CLOTH01_20240417_STORE_002_0034</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2024-04-18 00:00:00</t>
+          <t>2024-04-17 00:00:00</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6628,34 +6628,34 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
+          <t>DN_CLOTH01_20240418_STORE_001_000035</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
+          <t>CO_CLOTH01_20240418_STORE_001_0035</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6665,34 +6665,34 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
+          <t>DN_CLOTH01_20240418_STORE_001_000035</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
+          <t>CO_CLOTH01_20240418_STORE_001_0035</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6702,34 +6702,34 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
+          <t>DN_CLOTH01_20240418_STORE_001_000035</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
+          <t>CO_CLOTH01_20240418_STORE_001_0035</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6739,34 +6739,34 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
+          <t>DN_CLOTH01_20240418_STORE_001_000035</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
+          <t>CO_CLOTH01_20240418_STORE_001_0035</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6813,29 +6813,29 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
+          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
+          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6845,108 +6845,108 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2024-04-19 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
+          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
+          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2024-04-19 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
+          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
+          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2024-04-19 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
+          <t>DN_CLOTH01_20240418_STORE_002_000036</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
+          <t>CO_CLOTH01_20240418_STORE_002_0036</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6956,39 +6956,39 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2024-04-19 00:00:00</t>
+          <t>2024-04-18 00:00:00</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
+          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
+          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7005,27 +7005,27 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
+          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
+          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7042,27 +7042,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
+          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
+          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7079,27 +7079,27 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
+          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
+          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7116,27 +7116,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
+          <t>DN_CLOTH01_20240419_STORE_001_000037</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
+          <t>CO_CLOTH01_20240419_STORE_001_0037</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7153,32 +7153,32 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
+          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
+          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2024-04-20 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7190,32 +7190,32 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
+          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
+          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2024-04-20 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7227,32 +7227,32 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
+          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
+          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2024-04-20 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7264,22 +7264,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
+          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
+          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2024-04-20 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7301,32 +7301,32 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
+          <t>DN_CLOTH01_20240419_STORE_002_000038</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
+          <t>CO_CLOTH01_20240419_STORE_002_0038</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2024-04-20 00:00:00</t>
+          <t>2024-04-19 00:00:00</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7338,27 +7338,27 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
+          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
+          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7375,27 +7375,27 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
+          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
+          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7412,27 +7412,27 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
+          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
+          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7449,27 +7449,27 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
+          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
+          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7486,22 +7486,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
+          <t>DN_CLOTH01_20240420_STORE_001_000039</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
+          <t>CO_CLOTH01_20240420_STORE_001_0039</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7523,32 +7523,32 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
+          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
+          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2024-04-21 00:00:00</t>
+          <t>2024-04-20 00:00:00</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7560,32 +7560,32 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
+          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
+          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2024-04-21 00:00:00</t>
+          <t>2024-04-20 00:00:00</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7597,22 +7597,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
+          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
+          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2024-04-21 00:00:00</t>
+          <t>2024-04-20 00:00:00</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -7634,32 +7634,32 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
+          <t>DN_CLOTH01_20240420_STORE_002_000040</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
+          <t>CO_CLOTH01_20240420_STORE_002_0040</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2024-04-21 00:00:00</t>
+          <t>2024-04-20 00:00:00</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7701,34 +7701,34 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
+          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
+          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7738,34 +7738,34 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
+          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
+          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7775,34 +7775,34 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
+          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
+          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7812,34 +7812,34 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
+          <t>DN_CLOTH01_20240421_STORE_001_000041</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
+          <t>CO_CLOTH01_20240421_STORE_001_0041</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7849,39 +7849,39 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
+          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
+          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-21 00:00:00</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7893,32 +7893,32 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
+          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
+          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-21 00:00:00</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7930,32 +7930,32 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
+          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
+          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-21 00:00:00</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7967,32 +7967,32 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
+          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
+          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-21 00:00:00</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -8004,32 +8004,32 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
+          <t>DN_CLOTH01_20240421_STORE_002_000042</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
+          <t>CO_CLOTH01_20240421_STORE_002_0042</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2024-04-22 00:00:00</t>
+          <t>2024-04-21 00:00:00</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -8041,27 +8041,27 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
+          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
+          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8078,27 +8078,27 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
+          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
+          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8115,27 +8115,27 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
+          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
+          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8152,27 +8152,27 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
+          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
+          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -8189,22 +8189,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
+          <t>DN_CLOTH01_20240422_STORE_001_000043</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
+          <t>CO_CLOTH01_20240422_STORE_001_0043</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -8226,32 +8226,32 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
+          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
+          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -8263,32 +8263,32 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
+          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
+          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8300,32 +8300,32 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
+          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
+          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8337,32 +8337,32 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
+          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
+          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -8374,32 +8374,32 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
+          <t>DN_CLOTH01_20240422_STORE_002_000044</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
+          <t>CO_CLOTH01_20240422_STORE_002_0044</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2024-04-23 00:00:00</t>
+          <t>2024-04-22 00:00:00</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -8411,22 +8411,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
+          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
+          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8448,27 +8448,27 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
+          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
+          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8485,27 +8485,27 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
+          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
+          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8522,22 +8522,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
+          <t>DN_CLOTH01_20240423_STORE_001_000045</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
+          <t>CO_CLOTH01_20240423_STORE_001_0045</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8589,140 +8589,140 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
+          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
+          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
+          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
+          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
+          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
+          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
+          <t>DN_CLOTH01_20240423_STORE_002_000046</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
+          <t>CO_CLOTH01_20240423_STORE_002_0046</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2024-04-24 00:00:00</t>
+          <t>2024-04-23 00:00:00</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8774,34 +8774,34 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
+          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
+          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8811,34 +8811,34 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
+          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
+          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8848,34 +8848,34 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
+          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
+          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8885,34 +8885,34 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
+          <t>DN_CLOTH01_20240424_STORE_001_000047</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
+          <t>CO_CLOTH01_20240424_STORE_001_0047</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8944,12 +8944,12 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8959,182 +8959,182 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
+          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
+          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
+          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
+          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
+          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
+          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
+          <t>DN_CLOTH01_20240424_STORE_002_000048</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
+          <t>CO_CLOTH01_20240424_STORE_002_0048</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2024-04-24 00:00:00</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
+          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
+          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9151,27 +9151,27 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
+          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
+          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -9188,27 +9188,27 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
+          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
+          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9225,27 +9225,27 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
+          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
+          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9262,27 +9262,27 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
+          <t>DN_CLOTH01_20240425_STORE_001_000049</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
+          <t>CO_CLOTH01_20240425_STORE_001_0049</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -9299,32 +9299,32 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
+          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
+          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -9336,32 +9336,32 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
+          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
+          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -9373,32 +9373,32 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
+          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
+          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -9410,32 +9410,32 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
+          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
+          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -9447,12 +9447,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
+          <t>DN_CLOTH01_20240425_STORE_002_000050</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
+          <t>CO_CLOTH01_20240425_STORE_002_0050</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9462,49 +9462,49 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
+          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
+          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9514,34 +9514,34 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
+          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
+          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -9551,34 +9551,34 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
+          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
+          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9588,19 +9588,19 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
+          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
+          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9610,34 +9610,34 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
+          <t>DN_CLOTH01_20240426_STORE_001_000051</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
+          <t>CO_CLOTH01_20240426_STORE_001_0051</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9647,145 +9647,145 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
+          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
+          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
+          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
+          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
+          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
+          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
+          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
+          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9795,34 +9795,34 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
+          <t>DN_CLOTH01_20240426_STORE_002_000052</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
+          <t>CO_CLOTH01_20240426_STORE_002_0052</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9832,49 +9832,49 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2024-04-27 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
+          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
+          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9884,29 +9884,29 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
+          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
+          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -9921,56 +9921,56 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
+          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
+          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2024-04-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>2024-04-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9980,34 +9980,34 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2024-04-28 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+          <t>DN_CLOTH01_20240427_STORE_001_000053</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+          <t>CO_CLOTH01_20240427_STORE_001_0053</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10017,145 +10017,145 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2024-04-28 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2024-04-28 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2024-04-28 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>STORE_001</t>
+          <t>STORE_002</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ITM_BOT_0005</t>
+          <t>ITM_JEANS_BLUE_32</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2024-04-28 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_002_000056</t>
+          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_002_0056</t>
+          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10165,34 +10165,34 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_JEANS_BLUE_34</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2024-04-28 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_002_000056</t>
+          <t>DN_CLOTH01_20240427_STORE_002_000054</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_002_0056</t>
+          <t>CO_CLOTH01_20240427_STORE_002_0054</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10202,49 +10202,49 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ITM_BAS_0002</t>
+          <t>ITM_TEE_BASIC_M</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2024-04-28 00:00:00</t>
+          <t>2024-04-27 00:00:00</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_002_000056</t>
+          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_002_0056</t>
+          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>ITM_TOP_0003</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -10254,34 +10254,34 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>DN_CLOTH01_20240428_STORE_002_000056</t>
+          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>CO_CLOTH01_20240428_STORE_002_0056</t>
+          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>STORE_002</t>
+          <t>STORE_001</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ITM_TOP_0004</t>
+          <t>ITM_JEANS_BLUE_30</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -10291,44 +10291,266 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
+          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>STORE_001</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ITM_JEANS_BLUE_32</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2024-04-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>STORE_001</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ITM_JEANS_BLUE_34</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>2024-04-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>DN_CLOTH01_20240428_STORE_001_000055</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CO_CLOTH01_20240428_STORE_001_0055</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>STORE_001</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ITM_TEE_BASIC_M</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>2024-04-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>DN_CLOTH01_20240428_STORE_002_000056</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>CO_CLOTH01_20240428_STORE_002_0056</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>STORE_002</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>ITM_BOT_0005</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>STORE_002</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ITM_CHIPS_8OZ</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>2024-04-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>DN_CLOTH01_20240428_STORE_002_000056</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>CO_CLOTH01_20240428_STORE_002_0056</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>STORE_002</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ITM_JEANS_BLUE_30</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>2024-04-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>DN_CLOTH01_20240428_STORE_002_000056</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>CO_CLOTH01_20240428_STORE_002_0056</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>STORE_002</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ITM_JEANS_BLUE_32</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>2024-04-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>DN_CLOTH01_20240428_STORE_002_000056</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>CO_CLOTH01_20240428_STORE_002_0056</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>STORE_002</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ITM_TEE_BASIC_M</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
         <is>
           <t>2024-04-28 00:00:00</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>5</t>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
